--- a/human_resources_forms/009_hostess_registration_form--human_resources_forms.xlsx
+++ b/human_resources_forms/009_hostess_registration_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'event_host',_'value':_'event_host'}</t>
+          <t>event_host</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Event Host', 'value': 'Event Host'}</t>
+          <t>Event Host</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'day_operations',_'value':_'day_operations'}</t>
+          <t>day_operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Day Operations', 'value': 'Day Operations'}</t>
+          <t>Day Operations</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'part-time',_'value':_'part_time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Part-time', 'value': 'part_time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'full-time',_'value':_'full_time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Full-time', 'value': 'full_time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
